--- a/data/nzd0245/nzd0245.xlsx
+++ b/data/nzd0245/nzd0245.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M337"/>
+  <dimension ref="A1:M338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15581,6 +15581,51 @@
         <v>359.03</v>
       </c>
       <c r="M337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>371.16</v>
+      </c>
+      <c r="C338" t="n">
+        <v>348.63</v>
+      </c>
+      <c r="D338" t="n">
+        <v>347.09</v>
+      </c>
+      <c r="E338" t="n">
+        <v>344.25</v>
+      </c>
+      <c r="F338" t="n">
+        <v>343.86</v>
+      </c>
+      <c r="G338" t="n">
+        <v>345.38</v>
+      </c>
+      <c r="H338" t="n">
+        <v>353.32</v>
+      </c>
+      <c r="I338" t="n">
+        <v>359.29</v>
+      </c>
+      <c r="J338" t="n">
+        <v>354.67</v>
+      </c>
+      <c r="K338" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="L338" t="n">
+        <v>364.41</v>
+      </c>
+      <c r="M338" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15597,7 +15642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19160,6 +19205,16 @@
       </c>
       <c r="B356" t="n">
         <v>1.68</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -19328,28 +19383,28 @@
         <v>0.0255</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3702757426421861</v>
+        <v>0.3602004587631374</v>
       </c>
       <c r="J2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04303509535137384</v>
+        <v>0.04084521073216396</v>
       </c>
       <c r="M2" t="n">
-        <v>10.83060152526499</v>
+        <v>10.85698893684525</v>
       </c>
       <c r="N2" t="n">
-        <v>176.0841581369438</v>
+        <v>176.5162686777287</v>
       </c>
       <c r="O2" t="n">
-        <v>13.26967061147125</v>
+        <v>13.28594252124134</v>
       </c>
       <c r="P2" t="n">
-        <v>379.4361573649102</v>
+        <v>379.5372309804924</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19406,28 +19461,28 @@
         <v>0.046</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4550080769737602</v>
+        <v>0.4494345034071521</v>
       </c>
       <c r="J3" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K3" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07861182495834473</v>
+        <v>0.07713230733173515</v>
       </c>
       <c r="M3" t="n">
-        <v>9.296790469566591</v>
+        <v>9.300315858331489</v>
       </c>
       <c r="N3" t="n">
-        <v>139.3057902686004</v>
+        <v>139.1830794007578</v>
       </c>
       <c r="O3" t="n">
-        <v>11.80278739402691</v>
+        <v>11.79758786365916</v>
       </c>
       <c r="P3" t="n">
-        <v>346.6474535702727</v>
+        <v>346.7034368556375</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19484,28 +19539,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3505977341935263</v>
+        <v>0.3455470612475756</v>
       </c>
       <c r="J4" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05645844745563433</v>
+        <v>0.05514588244667662</v>
       </c>
       <c r="M4" t="n">
-        <v>8.589876930465048</v>
+        <v>8.589657202808016</v>
       </c>
       <c r="N4" t="n">
-        <v>117.9306005122066</v>
+        <v>117.8193377509997</v>
       </c>
       <c r="O4" t="n">
-        <v>10.8595856510369</v>
+        <v>10.85446165182777</v>
       </c>
       <c r="P4" t="n">
-        <v>346.9087540733804</v>
+        <v>346.9594851279611</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19562,28 +19617,28 @@
         <v>0.0306</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2851544875523432</v>
+        <v>0.2768551867310962</v>
       </c>
       <c r="J5" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K5" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03205746741401938</v>
+        <v>0.03032085710008725</v>
       </c>
       <c r="M5" t="n">
-        <v>9.518860299223801</v>
+        <v>9.534980406432856</v>
       </c>
       <c r="N5" t="n">
-        <v>140.4501636216004</v>
+        <v>140.6703043212959</v>
       </c>
       <c r="O5" t="n">
-        <v>11.85116718393595</v>
+        <v>11.8604512697155</v>
       </c>
       <c r="P5" t="n">
-        <v>351.464502060841</v>
+        <v>351.5482532500068</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19640,28 +19695,28 @@
         <v>0.0319</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2531109742278724</v>
+        <v>0.2428680293132204</v>
       </c>
       <c r="J6" t="n">
+        <v>337</v>
+      </c>
+      <c r="K6" t="n">
         <v>336</v>
       </c>
-      <c r="K6" t="n">
-        <v>335</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02345514882793798</v>
+        <v>0.02163066336799413</v>
       </c>
       <c r="M6" t="n">
-        <v>9.675133807391752</v>
+        <v>9.691263369979968</v>
       </c>
       <c r="N6" t="n">
-        <v>151.7135144975694</v>
+        <v>152.2308680588918</v>
       </c>
       <c r="O6" t="n">
-        <v>12.31720400486934</v>
+        <v>12.33818738951925</v>
       </c>
       <c r="P6" t="n">
-        <v>355.3472958379166</v>
+        <v>355.4509211968008</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19718,28 +19773,28 @@
         <v>0.0426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2986601395427735</v>
+        <v>0.2913844518318265</v>
       </c>
       <c r="J7" t="n">
+        <v>337</v>
+      </c>
+      <c r="K7" t="n">
         <v>336</v>
       </c>
-      <c r="K7" t="n">
-        <v>335</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.050463509688911</v>
+        <v>0.0481967050852169</v>
       </c>
       <c r="M7" t="n">
-        <v>7.809369798193933</v>
+        <v>7.816573994658171</v>
       </c>
       <c r="N7" t="n">
-        <v>96.60301774724505</v>
+        <v>96.81263736296299</v>
       </c>
       <c r="O7" t="n">
-        <v>9.828683418812769</v>
+        <v>9.839341307372308</v>
       </c>
       <c r="P7" t="n">
-        <v>350.5308223799212</v>
+        <v>350.6038337047993</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19796,28 +19851,28 @@
         <v>0.0378</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08452473890506149</v>
+        <v>0.08091435495313087</v>
       </c>
       <c r="J8" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K8" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004395411324993215</v>
+        <v>0.004048743168175162</v>
       </c>
       <c r="M8" t="n">
-        <v>7.748150808665605</v>
+        <v>7.743030586377325</v>
       </c>
       <c r="N8" t="n">
-        <v>93.37962315181107</v>
+        <v>93.22374434034894</v>
       </c>
       <c r="O8" t="n">
-        <v>9.663313259530144</v>
+        <v>9.655244395682015</v>
       </c>
       <c r="P8" t="n">
-        <v>357.5499886823897</v>
+        <v>357.5861873707617</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19874,28 +19929,28 @@
         <v>0.0317</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2453712129501324</v>
+        <v>-0.2470900317208866</v>
       </c>
       <c r="J9" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K9" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02303818695706061</v>
+        <v>0.0234905493812062</v>
       </c>
       <c r="M9" t="n">
-        <v>9.820065217076458</v>
+        <v>9.800443872682807</v>
       </c>
       <c r="N9" t="n">
-        <v>146.5725725285362</v>
+        <v>146.1652815660933</v>
       </c>
       <c r="O9" t="n">
-        <v>12.10671600924612</v>
+        <v>12.08988343889606</v>
       </c>
       <c r="P9" t="n">
-        <v>368.790373292717</v>
+        <v>368.807637821584</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -19952,28 +20007,28 @@
         <v>0.0313</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02205561448550331</v>
+        <v>0.01640787304936183</v>
       </c>
       <c r="J10" t="n">
+        <v>337</v>
+      </c>
+      <c r="K10" t="n">
         <v>336</v>
       </c>
-      <c r="K10" t="n">
-        <v>335</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0001653367281707618</v>
+        <v>9.191290741139557e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>9.478900763937306</v>
+        <v>9.478914901645963</v>
       </c>
       <c r="N10" t="n">
-        <v>167.3190887890579</v>
+        <v>167.1156732751186</v>
       </c>
       <c r="O10" t="n">
-        <v>12.93518800748786</v>
+        <v>12.92732274197247</v>
       </c>
       <c r="P10" t="n">
-        <v>364.082431742348</v>
+        <v>364.1395685558408</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20030,28 +20085,28 @@
         <v>0.0273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2176240247037839</v>
+        <v>-0.2174057923809966</v>
       </c>
       <c r="J11" t="n">
+        <v>337</v>
+      </c>
+      <c r="K11" t="n">
         <v>336</v>
       </c>
-      <c r="K11" t="n">
-        <v>335</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.01918613789167722</v>
+        <v>0.01926438954514464</v>
       </c>
       <c r="M11" t="n">
-        <v>9.188006432011756</v>
+        <v>9.161829352764588</v>
       </c>
       <c r="N11" t="n">
-        <v>137.7085882419891</v>
+        <v>137.2991810573095</v>
       </c>
       <c r="O11" t="n">
-        <v>11.7349302614881</v>
+        <v>11.71747332223588</v>
       </c>
       <c r="P11" t="n">
-        <v>373.0171953078768</v>
+        <v>373.0149875050469</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -20108,28 +20163,28 @@
         <v>0.0316</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1818636656066324</v>
+        <v>0.1806960018546194</v>
       </c>
       <c r="J12" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K12" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L12" t="n">
-        <v>0.009503646038930169</v>
+        <v>0.009439944299192371</v>
       </c>
       <c r="M12" t="n">
-        <v>11.0644593004699</v>
+        <v>11.03640991317416</v>
       </c>
       <c r="N12" t="n">
-        <v>195.4487402741215</v>
+        <v>194.8743634482162</v>
       </c>
       <c r="O12" t="n">
-        <v>13.98029828988357</v>
+        <v>13.95974080877637</v>
       </c>
       <c r="P12" t="n">
-        <v>361.6974142250807</v>
+        <v>361.7092874870163</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -20167,7 +20222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M337"/>
+  <dimension ref="A1:M338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42685,6 +42740,73 @@
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-38.10232173639125,174.76230622661996</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-38.101764939556084,174.7629207913388</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-38.10113027788191,174.7633172428855</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-38.100500432579665,174.7637272025558</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-38.09986149388727,174.7641117038889</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-38.099215464941736,174.76447635855408</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-38.09854561729986,174.764774304488</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-38.09788307143862,174.76509272147283</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-38.09725980040086,174.76552117628526</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>-38.09657105687983,174.76576623705625</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>-38.09594284147662,174.76618087243523</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0245/nzd0245.xlsx
+++ b/data/nzd0245/nzd0245.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M338"/>
+  <dimension ref="A1:M339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15626,6 +15626,51 @@
         <v>364.41</v>
       </c>
       <c r="M338" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>366.22</v>
+      </c>
+      <c r="C339" t="n">
+        <v>344.93</v>
+      </c>
+      <c r="D339" t="n">
+        <v>346.86</v>
+      </c>
+      <c r="E339" t="n">
+        <v>338.96</v>
+      </c>
+      <c r="F339" t="n">
+        <v>340.3</v>
+      </c>
+      <c r="G339" t="n">
+        <v>346.13</v>
+      </c>
+      <c r="H339" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="I339" t="n">
+        <v>359.27</v>
+      </c>
+      <c r="J339" t="n">
+        <v>351.82</v>
+      </c>
+      <c r="K339" t="n">
+        <v>368.48</v>
+      </c>
+      <c r="L339" t="n">
+        <v>368.81</v>
+      </c>
+      <c r="M339" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15642,7 +15687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19215,6 +19260,16 @@
       </c>
       <c r="B357" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -19383,28 +19438,28 @@
         <v>0.0255</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3602004587631374</v>
+        <v>0.3473262766813235</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04084521073216396</v>
+        <v>0.03799610666427877</v>
       </c>
       <c r="M2" t="n">
-        <v>10.85698893684525</v>
+        <v>10.9016360820448</v>
       </c>
       <c r="N2" t="n">
-        <v>176.5162686777287</v>
+        <v>177.5297148485157</v>
       </c>
       <c r="O2" t="n">
-        <v>13.28594252124134</v>
+        <v>13.32402772619885</v>
       </c>
       <c r="P2" t="n">
-        <v>379.5372309804924</v>
+        <v>379.6674767770552</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19461,28 +19516,28 @@
         <v>0.046</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4494345034071521</v>
+        <v>0.4417402293048318</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07713230733173515</v>
+        <v>0.07487151021594896</v>
       </c>
       <c r="M3" t="n">
-        <v>9.300315858331489</v>
+        <v>9.315595578594596</v>
       </c>
       <c r="N3" t="n">
-        <v>139.1830794007578</v>
+        <v>139.3161099415061</v>
       </c>
       <c r="O3" t="n">
-        <v>11.79758786365916</v>
+        <v>11.80322455693808</v>
       </c>
       <c r="P3" t="n">
-        <v>346.7034368556375</v>
+        <v>346.7813668588431</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19539,28 +19594,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3455470612475756</v>
+        <v>0.3403408277876911</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05514588244667662</v>
+        <v>0.05379528380922061</v>
       </c>
       <c r="M4" t="n">
-        <v>8.589657202808016</v>
+        <v>8.590162115573046</v>
       </c>
       <c r="N4" t="n">
-        <v>117.8193377509997</v>
+        <v>117.7201968242853</v>
       </c>
       <c r="O4" t="n">
-        <v>10.85446165182777</v>
+        <v>10.84989386235116</v>
       </c>
       <c r="P4" t="n">
-        <v>346.9594851279611</v>
+        <v>347.0122154810552</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19617,28 +19672,28 @@
         <v>0.0306</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2768551867310962</v>
+        <v>0.2655448043463871</v>
       </c>
       <c r="J5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K5" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03032085710008725</v>
+        <v>0.0279066847478352</v>
       </c>
       <c r="M5" t="n">
-        <v>9.534980406432856</v>
+        <v>9.568672299148444</v>
       </c>
       <c r="N5" t="n">
-        <v>140.6703043212959</v>
+        <v>141.4205493957672</v>
       </c>
       <c r="O5" t="n">
-        <v>11.8604512697155</v>
+        <v>11.89203722647079</v>
       </c>
       <c r="P5" t="n">
-        <v>351.5482532500068</v>
+        <v>351.6633454295789</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19695,28 +19750,28 @@
         <v>0.0319</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2428680293132204</v>
+        <v>0.230599075627248</v>
       </c>
       <c r="J6" t="n">
+        <v>338</v>
+      </c>
+      <c r="K6" t="n">
         <v>337</v>
       </c>
-      <c r="K6" t="n">
-        <v>336</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02163066336799413</v>
+        <v>0.0194907200883675</v>
       </c>
       <c r="M6" t="n">
-        <v>9.691263369979968</v>
+        <v>9.715229051520611</v>
       </c>
       <c r="N6" t="n">
-        <v>152.2308680588918</v>
+        <v>153.1462425344896</v>
       </c>
       <c r="O6" t="n">
-        <v>12.33818738951925</v>
+        <v>12.37522696900908</v>
       </c>
       <c r="P6" t="n">
-        <v>355.4509211968008</v>
+        <v>355.5760715656278</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19773,28 +19828,28 @@
         <v>0.0426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2913844518318265</v>
+        <v>0.2845221071724017</v>
       </c>
       <c r="J7" t="n">
+        <v>338</v>
+      </c>
+      <c r="K7" t="n">
         <v>337</v>
       </c>
-      <c r="K7" t="n">
-        <v>336</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0481967050852169</v>
+        <v>0.04613383373826141</v>
       </c>
       <c r="M7" t="n">
-        <v>7.816573994658171</v>
+        <v>7.821482530816617</v>
       </c>
       <c r="N7" t="n">
-        <v>96.81263736296299</v>
+        <v>96.96032000900247</v>
       </c>
       <c r="O7" t="n">
-        <v>9.839341307372308</v>
+        <v>9.846843149405929</v>
       </c>
       <c r="P7" t="n">
-        <v>350.6038337047993</v>
+        <v>350.6732752221091</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19851,28 +19906,28 @@
         <v>0.0378</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08091435495313087</v>
+        <v>0.07691813426903296</v>
       </c>
       <c r="J8" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K8" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004048743168175162</v>
+        <v>0.003677134197620058</v>
       </c>
       <c r="M8" t="n">
-        <v>7.743030586377325</v>
+        <v>7.739513575865317</v>
       </c>
       <c r="N8" t="n">
-        <v>93.22374434034894</v>
+        <v>93.09433821528403</v>
       </c>
       <c r="O8" t="n">
-        <v>9.655244395682015</v>
+        <v>9.648540729834954</v>
       </c>
       <c r="P8" t="n">
-        <v>357.5861873707617</v>
+        <v>357.6265926047576</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19929,28 +19984,28 @@
         <v>0.0317</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2470900317208866</v>
+        <v>-0.2487939804060824</v>
       </c>
       <c r="J9" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K9" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0234905493812062</v>
+        <v>0.02394952691469399</v>
       </c>
       <c r="M9" t="n">
-        <v>9.800443872682807</v>
+        <v>9.780706806124352</v>
       </c>
       <c r="N9" t="n">
-        <v>146.1652815660933</v>
+        <v>145.759559299172</v>
       </c>
       <c r="O9" t="n">
-        <v>12.08988343889606</v>
+        <v>12.07309236687817</v>
       </c>
       <c r="P9" t="n">
-        <v>368.807637821584</v>
+        <v>368.8248959442781</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20007,28 +20062,28 @@
         <v>0.0313</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01640787304936183</v>
+        <v>0.009152122680591096</v>
       </c>
       <c r="J10" t="n">
+        <v>338</v>
+      </c>
+      <c r="K10" t="n">
         <v>337</v>
       </c>
-      <c r="K10" t="n">
-        <v>336</v>
-      </c>
       <c r="L10" t="n">
-        <v>9.191290741139557e-05</v>
+        <v>2.869641014335844e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>9.478914901645963</v>
+        <v>9.486659233319273</v>
       </c>
       <c r="N10" t="n">
-        <v>167.1156732751186</v>
+        <v>167.0979147058674</v>
       </c>
       <c r="O10" t="n">
-        <v>12.92732274197247</v>
+        <v>12.92663586188871</v>
       </c>
       <c r="P10" t="n">
-        <v>364.1395685558408</v>
+        <v>364.2135813737233</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20085,28 +20140,28 @@
         <v>0.0273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2174057923809966</v>
+        <v>-0.2167192106302384</v>
       </c>
       <c r="J11" t="n">
+        <v>338</v>
+      </c>
+      <c r="K11" t="n">
         <v>337</v>
       </c>
-      <c r="K11" t="n">
-        <v>336</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.01926438954514464</v>
+        <v>0.01926299774364659</v>
       </c>
       <c r="M11" t="n">
-        <v>9.161829352764588</v>
+        <v>9.138246426709536</v>
       </c>
       <c r="N11" t="n">
-        <v>137.2991810573095</v>
+        <v>136.8960463255314</v>
       </c>
       <c r="O11" t="n">
-        <v>11.71747332223588</v>
+        <v>11.70025838712681</v>
       </c>
       <c r="P11" t="n">
-        <v>373.0149875050469</v>
+        <v>373.0079839771555</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -20163,28 +20218,28 @@
         <v>0.0316</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1806960018546194</v>
+        <v>0.1820297714428395</v>
       </c>
       <c r="J12" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K12" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L12" t="n">
-        <v>0.009439944299192371</v>
+        <v>0.009637464565590226</v>
       </c>
       <c r="M12" t="n">
-        <v>11.03640991317416</v>
+        <v>11.01140432112474</v>
       </c>
       <c r="N12" t="n">
-        <v>194.8743634482162</v>
+        <v>194.3070164882575</v>
       </c>
       <c r="O12" t="n">
-        <v>13.95974080877637</v>
+        <v>13.93940516981473</v>
       </c>
       <c r="P12" t="n">
-        <v>361.7092874870163</v>
+        <v>361.6956123525807</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -20222,7 +20277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M338"/>
+  <dimension ref="A1:M339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42807,6 +42862,73 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:26+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-38.10234006059537,174.76235755949307</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-38.10177866400975,174.7629592388227</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-38.10113113101893,174.76331963284568</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-38.10052005459629,174.76378217124403</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-38.0998746988025,174.76414869576166</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-38.0992126830201,174.76446856538558</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-38.098548139566184,174.7647813702344</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-38.09788314562263,174.76509292928716</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-38.09727037154804,174.76555078961647</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-38.096568163728776,174.76575813242962</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>-38.09592652123369,174.7661351543756</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0245/nzd0245.xlsx
+++ b/data/nzd0245/nzd0245.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M339"/>
+  <dimension ref="A1:M340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15638,7 +15638,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>366.22</v>
+        <v>370.9</v>
       </c>
       <c r="C339" t="n">
         <v>344.93</v>
@@ -15647,10 +15647,10 @@
         <v>346.86</v>
       </c>
       <c r="E339" t="n">
-        <v>338.96</v>
+        <v>345.09</v>
       </c>
       <c r="F339" t="n">
-        <v>340.3</v>
+        <v>346.4</v>
       </c>
       <c r="G339" t="n">
         <v>346.13</v>
@@ -15662,7 +15662,7 @@
         <v>359.27</v>
       </c>
       <c r="J339" t="n">
-        <v>351.82</v>
+        <v>358.54</v>
       </c>
       <c r="K339" t="n">
         <v>368.48</v>
@@ -15673,6 +15673,51 @@
       <c r="M339" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>378.02</v>
+      </c>
+      <c r="C340" t="n">
+        <v>350.6</v>
+      </c>
+      <c r="D340" t="n">
+        <v>352.83</v>
+      </c>
+      <c r="E340" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="F340" t="n">
+        <v>360.93</v>
+      </c>
+      <c r="G340" t="n">
+        <v>353.75</v>
+      </c>
+      <c r="H340" t="n">
+        <v>359.97</v>
+      </c>
+      <c r="I340" t="n">
+        <v>371.18</v>
+      </c>
+      <c r="J340" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="K340" t="n">
+        <v>384.87</v>
+      </c>
+      <c r="L340" t="n">
+        <v>378.82</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -15687,7 +15732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19270,6 +19315,16 @@
       </c>
       <c r="B358" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -19438,28 +19493,28 @@
         <v>0.0255</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3473262766813235</v>
+        <v>0.3438151023325658</v>
       </c>
       <c r="J2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03799610666427877</v>
+        <v>0.03753019108950206</v>
       </c>
       <c r="M2" t="n">
-        <v>10.9016360820448</v>
+        <v>10.89013705859011</v>
       </c>
       <c r="N2" t="n">
-        <v>177.5297148485157</v>
+        <v>176.7861453686836</v>
       </c>
       <c r="O2" t="n">
-        <v>13.32402772619885</v>
+        <v>13.29609511731484</v>
       </c>
       <c r="P2" t="n">
-        <v>379.6674767770552</v>
+        <v>379.703320030218</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19516,28 +19571,28 @@
         <v>0.046</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4417402293048318</v>
+        <v>0.4372863279792494</v>
       </c>
       <c r="J3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07487151021594896</v>
+        <v>0.07382074674766503</v>
       </c>
       <c r="M3" t="n">
-        <v>9.315595578594596</v>
+        <v>9.312597239809891</v>
       </c>
       <c r="N3" t="n">
-        <v>139.3161099415061</v>
+        <v>139.086930234047</v>
       </c>
       <c r="O3" t="n">
-        <v>11.80322455693808</v>
+        <v>11.79351220943308</v>
       </c>
       <c r="P3" t="n">
-        <v>346.7813668588431</v>
+        <v>346.8267070450518</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19594,28 +19649,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3403408277876911</v>
+        <v>0.3385302131231036</v>
       </c>
       <c r="J4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05379528380922061</v>
+        <v>0.05356072045320548</v>
       </c>
       <c r="M4" t="n">
-        <v>8.590162115573046</v>
+        <v>8.573908419530751</v>
       </c>
       <c r="N4" t="n">
-        <v>117.7201968242853</v>
+        <v>117.4029811611927</v>
       </c>
       <c r="O4" t="n">
-        <v>10.84989386235116</v>
+        <v>10.83526562485631</v>
       </c>
       <c r="P4" t="n">
-        <v>347.0122154810552</v>
+        <v>347.0306473231738</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19672,28 +19727,28 @@
         <v>0.0306</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2655448043463871</v>
+        <v>0.2675922896772772</v>
       </c>
       <c r="J5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K5" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0279066847478352</v>
+        <v>0.02861719696972176</v>
       </c>
       <c r="M5" t="n">
-        <v>9.568672299148444</v>
+        <v>9.528750150164093</v>
       </c>
       <c r="N5" t="n">
-        <v>141.4205493957672</v>
+        <v>140.410324964102</v>
       </c>
       <c r="O5" t="n">
-        <v>11.89203722647079</v>
+        <v>11.84948627426953</v>
       </c>
       <c r="P5" t="n">
-        <v>351.6633454295789</v>
+        <v>351.6425852203512</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19750,28 +19805,28 @@
         <v>0.0319</v>
       </c>
       <c r="I6" t="n">
-        <v>0.230599075627248</v>
+        <v>0.2336039226174729</v>
       </c>
       <c r="J6" t="n">
+        <v>339</v>
+      </c>
+      <c r="K6" t="n">
         <v>338</v>
       </c>
-      <c r="K6" t="n">
-        <v>337</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0194907200883675</v>
+        <v>0.02020174675415731</v>
       </c>
       <c r="M6" t="n">
-        <v>9.715229051520611</v>
+        <v>9.673589774215282</v>
       </c>
       <c r="N6" t="n">
-        <v>153.1462425344896</v>
+        <v>152.0332015622181</v>
       </c>
       <c r="O6" t="n">
-        <v>12.37522696900908</v>
+        <v>12.33017443356817</v>
       </c>
       <c r="P6" t="n">
-        <v>355.5760715656278</v>
+        <v>355.5454443374045</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19828,28 +19883,28 @@
         <v>0.0426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2845221071724017</v>
+        <v>0.2820020648152153</v>
       </c>
       <c r="J7" t="n">
+        <v>339</v>
+      </c>
+      <c r="K7" t="n">
         <v>338</v>
       </c>
-      <c r="K7" t="n">
-        <v>337</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.04613383373826141</v>
+        <v>0.04560439536287175</v>
       </c>
       <c r="M7" t="n">
-        <v>7.821482530816617</v>
+        <v>7.808732779030422</v>
       </c>
       <c r="N7" t="n">
-        <v>96.96032000900247</v>
+        <v>96.73186265363569</v>
       </c>
       <c r="O7" t="n">
-        <v>9.846843149405929</v>
+        <v>9.835235770109209</v>
       </c>
       <c r="P7" t="n">
-        <v>350.6732752221091</v>
+        <v>350.6989065508794</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19906,28 +19961,28 @@
         <v>0.0378</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07691813426903296</v>
+        <v>0.07708907461799594</v>
       </c>
       <c r="J8" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K8" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003677134197620058</v>
+        <v>0.003716652201770865</v>
       </c>
       <c r="M8" t="n">
-        <v>7.739513575865317</v>
+        <v>7.717504909105053</v>
       </c>
       <c r="N8" t="n">
-        <v>93.09433821528403</v>
+        <v>92.81836361495415</v>
       </c>
       <c r="O8" t="n">
-        <v>9.648540729834954</v>
+        <v>9.634228750395859</v>
       </c>
       <c r="P8" t="n">
-        <v>357.6265926047576</v>
+        <v>357.6248553625932</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19984,28 +20039,28 @@
         <v>0.0317</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2487939804060824</v>
+        <v>-0.2437390755604633</v>
       </c>
       <c r="J9" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K9" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02394952691469399</v>
+        <v>0.02311419737460318</v>
       </c>
       <c r="M9" t="n">
-        <v>9.780706806124352</v>
+        <v>9.777062749073185</v>
       </c>
       <c r="N9" t="n">
-        <v>145.759559299172</v>
+        <v>145.5637412538987</v>
       </c>
       <c r="O9" t="n">
-        <v>12.07309236687817</v>
+        <v>12.0649799524864</v>
       </c>
       <c r="P9" t="n">
-        <v>368.8248959442781</v>
+        <v>368.7734376136565</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20062,28 +20117,28 @@
         <v>0.0313</v>
       </c>
       <c r="I10" t="n">
-        <v>0.009152122680591096</v>
+        <v>0.01829773303611592</v>
       </c>
       <c r="J10" t="n">
+        <v>339</v>
+      </c>
+      <c r="K10" t="n">
         <v>338</v>
       </c>
-      <c r="K10" t="n">
-        <v>337</v>
-      </c>
       <c r="L10" t="n">
-        <v>2.869641014335844e-05</v>
+        <v>0.0001155014098636054</v>
       </c>
       <c r="M10" t="n">
-        <v>9.486659233319273</v>
+        <v>9.468660870451833</v>
       </c>
       <c r="N10" t="n">
-        <v>167.0979147058674</v>
+        <v>166.4897743090974</v>
       </c>
       <c r="O10" t="n">
-        <v>12.92663586188871</v>
+        <v>12.90309165700598</v>
       </c>
       <c r="P10" t="n">
-        <v>364.2135813737233</v>
+        <v>364.1200166702166</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20140,28 +20195,28 @@
         <v>0.0273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2167192106302384</v>
+        <v>-0.2066959654093291</v>
       </c>
       <c r="J11" t="n">
+        <v>339</v>
+      </c>
+      <c r="K11" t="n">
         <v>338</v>
       </c>
-      <c r="K11" t="n">
-        <v>337</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.01926299774364659</v>
+        <v>0.01754771260145238</v>
       </c>
       <c r="M11" t="n">
-        <v>9.138246426709536</v>
+        <v>9.163117479273716</v>
       </c>
       <c r="N11" t="n">
-        <v>136.8960463255314</v>
+        <v>137.3995767719604</v>
       </c>
       <c r="O11" t="n">
-        <v>11.70025838712681</v>
+        <v>11.72175655658999</v>
       </c>
       <c r="P11" t="n">
-        <v>373.0079839771555</v>
+        <v>372.9052247384159</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -20218,28 +20273,28 @@
         <v>0.0316</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1820297714428395</v>
+        <v>0.189072084348034</v>
       </c>
       <c r="J12" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K12" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L12" t="n">
-        <v>0.009637464565590226</v>
+        <v>0.01043115972268549</v>
       </c>
       <c r="M12" t="n">
-        <v>11.01140432112474</v>
+        <v>11.0205157563567</v>
       </c>
       <c r="N12" t="n">
-        <v>194.3070164882575</v>
+        <v>194.1741389066319</v>
       </c>
       <c r="O12" t="n">
-        <v>13.93940516981473</v>
+        <v>13.9346380974402</v>
       </c>
       <c r="P12" t="n">
-        <v>361.6956123525807</v>
+        <v>361.6230413850786</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -20277,7 +20332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M339"/>
+  <dimension ref="A1:M340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42870,7 +42925,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>-38.10234006059537,174.76235755949307</t>
+          <t>-38.10232270082363,174.76230892834948</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -42885,12 +42940,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>-38.10052005459629,174.76378217124403</t>
+          <t>-38.10049731679386,174.76371847407108</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>-38.0998746988025,174.76414869576166</t>
+          <t>-38.09985207239546,174.76408531081904</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -42910,7 +42965,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>-38.09727037154804,174.76555078961647</t>
+          <t>-38.097245445883445,174.76548096451197</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -42926,6 +42981,73 @@
       <c r="M339" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-38.10229629019091,174.76223494255007</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-38.10175763220655,174.7629003206571</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-38.10110898653252,174.76325759780948</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-38.10045599547614,174.76360271780618</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-38.099798176893714,174.76393433011714</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-38.099184418666134,174.76438938682608</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-38.098520950995756,174.76470520566912</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-38.09783896897569,174.7649691759231</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-38.097188584050926,174.76532167616514</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>-38.09650737033169,174.7655878315087</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>-38.09588939261271,174.76603114586374</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0245/nzd0245.xlsx
+++ b/data/nzd0245/nzd0245.xlsx
@@ -15732,7 +15732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19325,6 +19325,16 @@
       </c>
       <c r="B359" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0245/nzd0245.xlsx
+++ b/data/nzd0245/nzd0245.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M340"/>
+  <dimension ref="A1:M343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15718,6 +15718,141 @@
       <c r="M340" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>383.11</v>
+      </c>
+      <c r="C341" t="n">
+        <v>355.3</v>
+      </c>
+      <c r="D341" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="E341" t="n">
+        <v>363.31</v>
+      </c>
+      <c r="F341" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="G341" t="n">
+        <v>359.05</v>
+      </c>
+      <c r="H341" t="n">
+        <v>365.5</v>
+      </c>
+      <c r="I341" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="J341" t="n">
+        <v>379.91</v>
+      </c>
+      <c r="K341" t="n">
+        <v>389.02</v>
+      </c>
+      <c r="L341" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>383.38</v>
+      </c>
+      <c r="C342" t="n">
+        <v>352.75</v>
+      </c>
+      <c r="D342" t="n">
+        <v>353</v>
+      </c>
+      <c r="E342" t="n">
+        <v>364.88</v>
+      </c>
+      <c r="F342" t="n">
+        <v>360.46</v>
+      </c>
+      <c r="G342" t="n">
+        <v>357.43</v>
+      </c>
+      <c r="H342" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="I342" t="n">
+        <v>370.01</v>
+      </c>
+      <c r="J342" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="K342" t="n">
+        <v>387.4</v>
+      </c>
+      <c r="L342" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>385.91</v>
+      </c>
+      <c r="C343" t="n">
+        <v>355.5</v>
+      </c>
+      <c r="D343" t="n">
+        <v>356.08</v>
+      </c>
+      <c r="E343" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="F343" t="n">
+        <v>360.46</v>
+      </c>
+      <c r="G343" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="H343" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="I343" t="n">
+        <v>372.92</v>
+      </c>
+      <c r="J343" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="K343" t="n">
+        <v>389.61</v>
+      </c>
+      <c r="L343" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B360"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19335,6 +19470,36 @@
       </c>
       <c r="B360" t="n">
         <v>-0.01</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -19503,28 +19668,28 @@
         <v>0.0255</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3438151023325658</v>
+        <v>0.3359411342811278</v>
       </c>
       <c r="J2" t="n">
+        <v>342</v>
+      </c>
+      <c r="K2" t="n">
         <v>339</v>
       </c>
-      <c r="K2" t="n">
-        <v>336</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.03753019108950206</v>
+        <v>0.0365078381891295</v>
       </c>
       <c r="M2" t="n">
-        <v>10.89013705859011</v>
+        <v>10.84015822959268</v>
       </c>
       <c r="N2" t="n">
-        <v>176.7861453686836</v>
+        <v>175.4278660892397</v>
       </c>
       <c r="O2" t="n">
-        <v>13.29609511731484</v>
+        <v>13.24491850066431</v>
       </c>
       <c r="P2" t="n">
-        <v>379.703320030218</v>
+        <v>379.7838620445822</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19581,28 +19746,28 @@
         <v>0.046</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4372863279792494</v>
+        <v>0.4306886891664277</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07382074674766503</v>
+        <v>0.07296595588460109</v>
       </c>
       <c r="M3" t="n">
-        <v>9.312597239809891</v>
+        <v>9.266902706575499</v>
       </c>
       <c r="N3" t="n">
-        <v>139.086930234047</v>
+        <v>138.0141931033213</v>
       </c>
       <c r="O3" t="n">
-        <v>11.79351220943308</v>
+        <v>11.74794420753356</v>
       </c>
       <c r="P3" t="n">
-        <v>346.8267070450518</v>
+        <v>346.8942723972086</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19659,28 +19824,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3385302131231036</v>
+        <v>0.3369186291156906</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05356072045320548</v>
+        <v>0.05402538540310253</v>
       </c>
       <c r="M4" t="n">
-        <v>8.573908419530751</v>
+        <v>8.507782595493888</v>
       </c>
       <c r="N4" t="n">
-        <v>117.4029811611927</v>
+        <v>116.4000238193083</v>
       </c>
       <c r="O4" t="n">
-        <v>10.83526562485631</v>
+        <v>10.78888427129091</v>
       </c>
       <c r="P4" t="n">
-        <v>347.0306473231738</v>
+        <v>347.0471520717768</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19737,28 +19902,28 @@
         <v>0.0306</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2675922896772772</v>
+        <v>0.2784498360502818</v>
       </c>
       <c r="J5" t="n">
+        <v>342</v>
+      </c>
+      <c r="K5" t="n">
         <v>339</v>
       </c>
-      <c r="K5" t="n">
-        <v>336</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.02861719696972176</v>
+        <v>0.03140189246415859</v>
       </c>
       <c r="M5" t="n">
-        <v>9.528750150164093</v>
+        <v>9.498292221651685</v>
       </c>
       <c r="N5" t="n">
-        <v>140.410324964102</v>
+        <v>139.5533318391952</v>
       </c>
       <c r="O5" t="n">
-        <v>11.84948627426953</v>
+        <v>11.81326931205732</v>
       </c>
       <c r="P5" t="n">
-        <v>351.6425852203512</v>
+        <v>351.5308452368201</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19815,28 +19980,28 @@
         <v>0.0319</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2336039226174729</v>
+        <v>0.2350402416634758</v>
       </c>
       <c r="J6" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K6" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02020174675415731</v>
+        <v>0.02081743042052475</v>
       </c>
       <c r="M6" t="n">
-        <v>9.673589774215282</v>
+        <v>9.612785708032975</v>
       </c>
       <c r="N6" t="n">
-        <v>152.0332015622181</v>
+        <v>150.7844173127467</v>
       </c>
       <c r="O6" t="n">
-        <v>12.33017443356817</v>
+        <v>12.27943065914486</v>
       </c>
       <c r="P6" t="n">
-        <v>355.5454443374045</v>
+        <v>355.5306690000902</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19893,28 +20058,28 @@
         <v>0.0426</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2820020648152153</v>
+        <v>0.2830092320258828</v>
       </c>
       <c r="J7" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K7" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04560439536287175</v>
+        <v>0.04674419201674707</v>
       </c>
       <c r="M7" t="n">
-        <v>7.808732779030422</v>
+        <v>7.750945386100345</v>
       </c>
       <c r="N7" t="n">
-        <v>96.73186265363569</v>
+        <v>95.89356623249317</v>
       </c>
       <c r="O7" t="n">
-        <v>9.835235770109209</v>
+        <v>9.792526039408482</v>
       </c>
       <c r="P7" t="n">
-        <v>350.6989065508794</v>
+        <v>350.6885956697992</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19971,28 +20136,28 @@
         <v>0.0378</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07708907461799594</v>
+        <v>0.08176975504152084</v>
       </c>
       <c r="J8" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K8" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003716652201770865</v>
+        <v>0.004254024258358857</v>
       </c>
       <c r="M8" t="n">
-        <v>7.717504909105053</v>
+        <v>7.675136337029397</v>
       </c>
       <c r="N8" t="n">
-        <v>92.81836361495415</v>
+        <v>92.10720496190868</v>
       </c>
       <c r="O8" t="n">
-        <v>9.634228750395859</v>
+        <v>9.597249864513723</v>
       </c>
       <c r="P8" t="n">
-        <v>357.6248553625932</v>
+        <v>357.5770240175165</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20049,28 +20214,28 @@
         <v>0.0317</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2437390755604633</v>
+        <v>-0.226351550799771</v>
       </c>
       <c r="J9" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K9" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02311419737460318</v>
+        <v>0.02023855690740795</v>
       </c>
       <c r="M9" t="n">
-        <v>9.777062749073185</v>
+        <v>9.776406330840619</v>
       </c>
       <c r="N9" t="n">
-        <v>145.5637412538987</v>
+        <v>145.2543548293256</v>
       </c>
       <c r="O9" t="n">
-        <v>12.0649799524864</v>
+        <v>12.05215146060344</v>
       </c>
       <c r="P9" t="n">
-        <v>368.7734376136565</v>
+        <v>368.5953850174558</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20127,28 +20292,28 @@
         <v>0.0313</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01829773303611592</v>
+        <v>0.04153902890195475</v>
       </c>
       <c r="J10" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K10" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001155014098636054</v>
+        <v>0.0006003750632230798</v>
       </c>
       <c r="M10" t="n">
-        <v>9.468660870451833</v>
+        <v>9.5124834309135</v>
       </c>
       <c r="N10" t="n">
-        <v>166.4897743090974</v>
+        <v>166.6727785226929</v>
       </c>
       <c r="O10" t="n">
-        <v>12.90309165700598</v>
+        <v>12.91018119635402</v>
       </c>
       <c r="P10" t="n">
-        <v>364.1200166702166</v>
+        <v>363.8803350209457</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20205,28 +20370,28 @@
         <v>0.0273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2066959654093291</v>
+        <v>-0.1709321471815009</v>
       </c>
       <c r="J11" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K11" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01754771260145238</v>
+        <v>0.01195933027676488</v>
       </c>
       <c r="M11" t="n">
-        <v>9.163117479273716</v>
+        <v>9.266544971579169</v>
       </c>
       <c r="N11" t="n">
-        <v>137.3995767719604</v>
+        <v>140.0718670897962</v>
       </c>
       <c r="O11" t="n">
-        <v>11.72175655658999</v>
+        <v>11.83519611539227</v>
       </c>
       <c r="P11" t="n">
-        <v>372.9052247384159</v>
+        <v>372.5363836843092</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -20283,28 +20448,28 @@
         <v>0.0316</v>
       </c>
       <c r="I12" t="n">
-        <v>0.189072084348034</v>
+        <v>0.1969273550492194</v>
       </c>
       <c r="J12" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K12" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01043115972268549</v>
+        <v>0.01149844270335565</v>
       </c>
       <c r="M12" t="n">
-        <v>11.0205157563567</v>
+        <v>10.96904990673607</v>
       </c>
       <c r="N12" t="n">
-        <v>194.1741389066319</v>
+        <v>192.8159658911778</v>
       </c>
       <c r="O12" t="n">
-        <v>13.9346380974402</v>
+        <v>13.88581887722787</v>
       </c>
       <c r="P12" t="n">
-        <v>361.6230413850786</v>
+        <v>361.5416648562486</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -20342,7 +20507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M340"/>
+  <dimension ref="A1:M343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43061,6 +43226,207 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-38.10227740952655,174.76218205104828</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-38.10174019841361,174.76285148199094</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-38.101096634568144,174.7632229953679</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-38.10042973375171,174.7635291492585</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-38.09977584710898,174.76387177657918</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-38.099164759699825,174.76433431515963</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-38.098500438984665,174.7646477445805</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-38.09782405793605,174.76492740529898</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-38.097166180501965,174.76525891683028</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-38.0964919772103,174.7655447108188</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-38.09589373232655,174.76604330269748</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-38.10227640799751,174.7621792454094</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-38.1017496571762,174.76287797956235</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-38.101108355952015,174.7632558313182</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-38.10042391017079,174.76351283533612</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-38.09979992024755,174.76393921386668</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-38.099170768669715,174.76435114838293</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-38.09851716758904,174.7646946070573</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-38.097843308753,174.76498133304815</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-38.09717660334941,174.7652881144632</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-38.09649798609337,174.76556154347156</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-38.09592900636278,174.76614211598798</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-38.10226702329604,174.76215295553794</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-38.10173945654961,174.76284940375032</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-38.10109693131215,174.76322382665768</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-38.1004141918331,174.76348561083427</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-38.09979992024755,174.76393921386668</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-38.09916138428974,174.76432485946125</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-38.09851716758904,174.7646946070573</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-38.09783251494549,174.7649510960987</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-38.09717215231226,174.76527564572217</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-38.09648978878931,174.76553858040887</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-38.09592900636278,174.76614211598798</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
